--- a/secure_report/XSS対応_手動テスト手順書.xlsx
+++ b/secure_report/XSS対応_手動テスト手順書.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="295">
   <si>
     <t>XSS対応 手動テスト手順書(メール送信・決済まわり)</t>
   </si>
@@ -496,7 +496,7 @@
   <si>
     <t xml:space="preserve">【やってはいけない】
 ・実在する銀行振込の注文の「注文No・商品ID・金額」を正しく組み合わせたCSVを作ること。入金処理が実行され、その受講者に入金完了メールが届く。
-・計画ExcelのP14(SQLの記号)のような、シングルクォートや「OR 1=1」を含む値を注文No・商品IDに入れること。この画面は入力値をそのままデータベースの問い合わせに使っており、他の注文に当たってしまう危険がある(開発者向けメモ参照)。</t>
+・計画ExcelのP14(SQLの記号)のような、シングルクォートや「OR 1=1」を含む値を注文No・商品IDに入れること。この画面の入力値のSQL連結は 2026-10-08 に修正済み(B-15)ですが、念のため、注文Noの欄にはSQLの記号を入れない運用とします。</t>
   </si>
   <si>
     <t>後片付け</t>
@@ -679,7 +679,7 @@
 毎回、商品を選び直して銀行振込の画面まで進めてから、Console(1行ずつ):
   var c=document.querySelector('[name=claim_flg]'); c.checked=true; c.value = prompt('貼り付け')
 確定ボタンを押す。貼り付ける値(1回ごとに注文は1件できる): abc / 1.5 / -1 / 99999999999999999999 / 計画Excel C-0420の「主:」文字列。
-※ シングルクォート( ' )を含む値は、データベースのエラーになる可能性がある(開発者向けメモ参照)。その場合は、画面に出たメッセージを備考に書いて「NG」にして連絡。</t>
+(claim_flg は 2026-10-08 に 0・1 のみに限定済み(B-16)。範囲外の値は拒否される想定です。)</t>
   </si>
   <si>
     <t>不正な値は保存されず、エラーか既定値(0)になる。500エラー・SQLエラーが出ない。alertが出ない。</t>
@@ -761,7 +761,7 @@
     <t>何も表示されない、またはエラー画面/トップに戻る。「order err.1」のような確認用の文字が出ない。</t>
   </si>
   <si>
-    <t>【現在のソースでは、上の10本すべてで「order err.1」と表示される作りです】表示されたらNG。1本ずつ、URLを備考に書く。</t>
+    <t>【2026-10-09 時点: 開発側で修正済み(B-19)。10本とも何も表示されない状態です】「order err」などの文字が出たらNG。1本ずつ、URLを備考に書く。</t>
   </si>
   <si>
     <t>settlement/end*.php</t>
@@ -839,10 +839,17 @@
 ・pay/nopay/cancel/nocancel + csrf_token 改ざん/空/無し(order_detail_id=99999999): すべて403で終了。
 ・mode にタグ付き文字列・x を送る: 通常画面のまま。画面に反映されない。
 【別エラー】mode が許可値以外(例: x)のとき、csrf_token が改ざん値・無しでも403にならず処理される(csrf検証は許可値のときだけ)。mode が空でなければ注文のステータス再計算(tbl_order の UPDATE)が走るため、CSRFなしで支払日が書き換わる恐れ(開発者向けメモ7番)。今回の注文は未入金のため、再計算しても値は変わらなかった。
-※入金済に変更(mode=pay)の正規操作は未実施(メールが飛ぶため。2026-10-09に持ち越し)。</t>
+※入金済に変更(mode=pay)の正規操作は未実施(メールが飛ぶため。2026-10-09に持ち越し)。
+【2026-10-09 再確認】開発側の修正(B-18。mode が指定されたら csrf を検証、許可値以外は処理しない)はリポジトリに入っているが、stg2 では未反映のまま: mode=x を csrf_token 改ざん・無しで送ると、まだ403にならず200で処理される。stg2への反映後に再確認する(それまで「OKだけど別エラー」のまま)。</t>
   </si>
   <si>
     <t>[CMS]bank_upload csv_upload</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">XSSは確認範囲で出ない(OK)。CSVを送信して確認(Chrome操作)。
@@ -851,7 +858,8 @@
 ・ファイル名(" &lt; ' ; ../ 300文字 日本語を含む)は画面に出ない。
 ・CSVの中身にHTMLタグ/=1+1/SVGを入れても、タグとして出る箇所なし。
 【別エラー】入金日が数字でないCSV(例: abc)を送ると500エラーになり、サーバー内部パスとスタックトレース(bank_upload/index.php:130 checkdate()のTypeError)が画面に出る(不具合まとめの[B-3]と同系統)。
-※アップロードしたCSV(約10本)がサーバー上に残っている。削除は開発担当に依頼。</t>
+※アップロードしたCSV(約10本)がサーバー上に残っている。削除は開発担当に依頼。
+【2026-10-09 再確認】別エラーは解消(B-15・B-20 がstg2に反映済み)。入金日が数字でないCSV(abc)は500にならず「入金日は「YYYY/MM/DD」の形式で…」のエラー表示。引用符の閉じ忘れ等(列数不正)は「列数が正しくありません。…4列で…」のエラー表示(「0件登録しました」は出ない)。→ OKに変更。</t>
   </si>
   <si>
     <t>[CMS]bank_upload 表示</t>
@@ -864,16 +872,17 @@
   </si>
   <si>
     <t>settlement/ 決済会社からの戻り</t>
-  </si>
-  <si>
-    <t>OK</t>
   </si>
   <si>
     <t xml:space="preserve">/settlement/ の完了画面15本(end.php・end_bank・end_card・end_free・end_passport_user・end_au 等)を、受講者ログイン済みのChromeでGET。order_id・OrderID・error・err_msg・amount・ErrCode に P02・P05・P19相当の文字列(目印XG12)を付けて確認。応答にXG12が出力されず、タグとして出る箇所もなし(15本とも)。完了画面はURLの値を使わず、セッション・DBから表示する作り。
 </t>
   </si>
   <si>
-    <t/>
+    <t>決済手段選択の画面 payment_*.php(10本)の「order err」出力は、ソース上すべてコメントアウト済み。実機では、決済を伴うため直接は開いていない(ソース確認)。完了画面 end_*.php 側の「order err.1」も、B-19 で修正され、stg2に反映済み(E-53 参照)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">決済完了画面 end_*.php の10本(au・cvs・docomo・edy・id・payeasy・paypal・sb・suica・webmoney)を、受講者ログイン済みのChromeで直接GET(Chrome操作)。2026-10-09 時点で、10本とも何も表示されない(中身が空)。確認用出力(SQL・var_dump・order err)なし。end.php・end_bank.php・end_card.php・end_free.php・end_passport_user.php も確認用出力なし。
+経緯: 2026-10-08 の確認では10本で「order err.1」が出ていた(開発の修正記録No.6の対象の取り違え)。開発側が B-19 で修正し、stg2に反映済み。</t>
   </si>
   <si>
     <t>alert_passport.php passport_pop_flg</t>
@@ -889,16 +898,15 @@
   </si>
   <si>
     <t>settlement/index.php hidden項目</t>
-  </si>
-  <si>
-    <t>要確認</t>
   </si>
   <si>
     <t xml:space="preserve">購入内容の確認画面(settlement/index.php)の隠し項目を、Chromeで書き換えて確認。
 ・csrf_token(order_regist.php / index.php): 改ざん値・空とも403で終了。注文・メールなし。
 ・pid: タグ付き文字列・JS脱出系・99999999・-1・abc・巨大数のいずれも「決済エラー」の固定画面。送った値は画面に出ない。内部パス等の漏れなし。
 ・temp_date / temp_no は未実施: 有効なcsrf_tokenで送ると、0円カートではそのまま注文が作られ無料の完了処理に進むため(メール系のため2026-10-09に持ち越し)。ソース上は、SQLにそのまま連結されている(order_regist.php:178,229)。
-・payment_type: 0円カートでは12に上書きされるため、改ざんが効かず検証にならない。check: 画面側で使われていない。</t>
+・payment_type: 0円カートでは12に上書きされるため、改ざんが効かず検証にならない。check: 画面側で使われていない。
+【2026-10-09 再確認】開発側の修正(B-17。temp_date・temp_no を数字だけに限定)がstg2に反映済み。temp_no=数字以外、temp_date=タグ付き・数字以外、シングルクォート入り、空、配列(temp_no[]・temp_date[])を、有効なcsrf_tokenで order_regist.php に送ったところ、すべて「決済エラー」の固定画面で拒否された(値は画面に出ない・内部パス等の漏れなし)。→ 未実施だった temp_date・temp_no の確認が完了したためOKに変更。
+※確認中、重複キー(temp_no=1&amp;temp_no=2。配列ではない)を1回送ってしまい、有効な値として通り、注文の仮データ(tbl_order_temp。order_no 202610092・0円)が1件作られた(完了処理には進めていない・メールなし)。</t>
   </si>
   <si>
     <t>settlement/index.php 表示</t>
@@ -912,7 +920,8 @@
   <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 claim_flg を送る注文確定の処理まで届かない。ソース上は、値がSQLのUPDATEにそのまま連結されている(payment_bank.php:145。開発者向けメモ参照)。
-【XSSの観点】ソース上は問題なし。claim_flg はCMSで ○/× の判定にしか使われず、値そのものは画面に出ない(amount_order/info.tpl・index.tpl)。決済画面(PC/スマホ)の動的な出力は、すべて |escape を通している。</t>
+【XSSの観点】ソース上は問題なし。claim_flg はCMSで ○/× の判定にしか使われず、値そのものは画面に出ない(amount_order/info.tpl・index.tpl)。決済画面(PC/スマホ)の動的な出力は、すべて |escape を通している。
+【2026-10-09】claim_flg のSQL連結は、開発側で 0・1 のみに限定済み(B-16)。stg2では、有料商品が無く到達できないため未確認。</t>
   </si>
   <si>
     <t>payment_bank.php hidden項目</t>
@@ -957,7 +966,8 @@
   <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 claim_flg を送る処理まで届かない。ソース上は、値がSQLのUPDATEにそのまま連結されている(payment_card.php:164。開発者向けメモ参照)。
-【XSSの観点】ソース上は問題なし。claim_flg はCMSで ○/× の判定にしか使われず、値そのものは画面に出ない。決済画面(PC/スマホ)の動的な出力は、すべて |escape を通している。</t>
+【XSSの観点】ソース上は問題なし。claim_flg はCMSで ○/× の判定にしか使われず、値そのものは画面に出ない。決済画面(PC/スマホ)の動的な出力は、すべて |escape を通している。
+【2026-10-09】claim_flg のSQL連結は、開発側で 0・1 のみに限定済み(B-16)。stg2では、有料商品が無く到達できないため未確認。</t>
   </si>
   <si>
     <t>payment_card.php hidden項目</t>
@@ -999,7 +1009,8 @@
     <t>alflearning/alflearning-cms/alfproduct/bank_upload/index.php の注文・注文詳細を引くSELECT</t>
   </si>
   <si>
-    <t>【要修正】「OR 1=1」を含む値で他人の注文に当たり、入金処理と入金完了メールが実在の受講者に飛ぶ恐れ。プレースホルダ/エスケープに修正。※ソースからの判断で、実機では攻撃していない(テスターにはSQL記号を入れないよう指示済み)。</t>
+    <t xml:space="preserve">【修正済み(B-15。コミット1f603af)】stg2に反映済み。
+(元の記載)【要修正】「OR 1=1」を含む値で他人の注文に当たり、入金処理と入金完了メールが実在の受講者に飛ぶ恐れ。プレースホルダ/エスケープに修正。※ソースからの判断で、実機では攻撃していない(テスターにはSQL記号を入れないよう指示済み)。</t>
   </si>
   <si>
     <t>入金日が数字でないCSV(例: abc)を送ると、checkdate()のTypeError(PHP8)で500エラーになり、画面にサーバー内部パスとスタックトレースが出る。</t>
@@ -1008,7 +1019,8 @@
     <t>bank_upload/index.php:130 (checkdate)。実機で確認済み(2026-10-08)</t>
   </si>
   <si>
-    <t>【要修正】入金日の形式チェックを、checkdate() の前に行う。不具合まとめの [B-3](エラー画面に内部パス)と同系統。</t>
+    <t xml:space="preserve">【修正済み(B-15・B-20。コミット1f603af)】stg2で、500にならずエラー表示になることを確認(2026-10-09)。
+(元の記載)【要修正】入金日の形式チェックを、checkdate() の前に行う。不具合まとめの [B-3](エラー画面に内部パス)と同系統。</t>
   </si>
   <si>
     <t>引用符の閉じ忘れなど、不正な形のCSVでも「合計0件の銀行振込を登録しました。」と表示される(0件なので更新もメールもない)。</t>
@@ -1017,7 +1029,8 @@
     <t>bank_upload/index.php (列数が4でない行を読み飛ばし、エラーにしない)。実機で確認済み(2026-10-08)</t>
   </si>
   <si>
-    <t>【要修正(低)】列数が合わない行は、エラーとして表示する。担当者が「登録できた」と誤解する恐れ。</t>
+    <t xml:space="preserve">【修正済み(B-20。コミット1f603af)】stg2で、列数不正のエラー表示になることを確認(2026-10-09)。
+(元の記載)【要修正(低)】列数が合わない行は、エラーとして表示する。担当者が「登録できた」と誤解する恐れ。</t>
   </si>
   <si>
     <t>「請求書の送付を希望する」claim_flg が、検証なしでそのままSQLのUPDATEに連結されている。</t>
@@ -1026,7 +1039,8 @@
     <t>alfproduct/public/settlement/payment_bank.php:145 / payment_card.php:164</t>
   </si>
   <si>
-    <t>【要修正】0/1のみ許可+エスケープ。数字以外やシングルクォートを入れるとSQLエラー/不正な値の保存になる見込み(C-0420・C-0426がNGになる見込み)。※ソースからの判断。実機は未確認。</t>
+    <t xml:space="preserve">【修正済み(B-16。コミット1f603af)】stg2は、有料商品が無く未確認。
+(元の記載)【要修正】0/1のみ許可+エスケープ。数字以外やシングルクォートを入れるとSQLエラー/不正な値の保存になる見込み(C-0420・C-0426がNGになる見込み)。※ソースからの判断。実機は未確認。</t>
   </si>
   <si>
     <t>決済完了画面 end_*.php の10本(au・cvs・docomo・edy・id・payeasy・paypal・sb・suica・webmoney)が、注文が見つからないとき「order err.1」と出力する。</t>
@@ -1035,7 +1049,8 @@
     <t>alfproduct/public/settlement/end_*.php (実機で確認済み 2026-10-08)</t>
   </si>
   <si>
-    <t>【開発に確認中】E-05 の期待結果は「エラー番号の文言が出ない」。開発の修正記録(No.6)は「決済完了画面10本のorder errをコメントアウト」だが、実際にコメントアウトされていたのは payment_*.php 側だった。対象の取り違えの可能性。</t>
+    <t xml:space="preserve">【修正済み(B-19。コミット1f603af)】stg2で、10本とも何も表示されないことを確認(2026-10-09)。
+(元の記載)【開発に確認中】E-05 の期待結果は「エラー番号の文言が出ない」。開発の修正記録(No.6)は「決済完了画面10本のorder errをコメントアウト」だが、実際にコメントアウトされていたのは payment_*.php 側だった。対象の取り違えの可能性。</t>
   </si>
   <si>
     <t>購入手続きの隠し項目 temp_date・temp_no が、エスケープなしでSQLに連結されている(select の where と insert の values の2か所)。</t>
@@ -1044,7 +1059,8 @@
     <t>alfproduct/public/settlement/order_regist.php:178 / :229</t>
   </si>
   <si>
-    <t>【要修正】数字のみ許可+エスケープ。ログイン済みの受講者が、注文番号の欄にSQLを混ぜられる恐れ。※ソースからの判断。実機では攻撃していない(送ると注文が作られるため)。</t>
+    <t xml:space="preserve">【修正済み(B-17。コミット1f603af)】stg2で、数字以外・配列などが拒否されることを確認(2026-10-09)。
+(元の記載)【要修正】数字のみ許可+エスケープ。ログイン済みの受講者が、注文番号の欄にSQLを混ぜられる恐れ。※ソースからの判断。実機では攻撃していない(送ると注文が作られるため)。</t>
   </si>
   <si>
     <t>注文詳細(amount_order/info.php)で、mode が許可値(pay・nopay・cancel・nocancel)以外でも、空でなければ、注文全体のステータス再計算(tbl_order の UPDATE。全明細が入金済みなら payment_date を現在時刻で上書き)が走る。csrf_token の検証は、許可値のときだけ行われる。</t>
@@ -1053,7 +1069,8 @@
     <t>alflearning/alflearning-cms/alfproduct/amount_order/info.php:94-96(csrf検証は許可値のみ)、:211-371(mode が空でなければ再計算)</t>
   </si>
   <si>
-    <t>【要修正】mode が許可値以外のときも、csrf検証を行うか、再計算を許可値のときだけにする。CSRFなしで、注文の支払日を書き換えられる恐れ。※実機で一部確認(2026-10-08): mode=x を csrf_token 改ざん・無しで送ると、403にならず処理された。注文が未入金だったため、再計算で値は変わらなかった(入金済の注文では、payment_date が上書きされる見込み。実在の会員の注文では試していない)。</t>
+    <t xml:space="preserve">【修正はリポジトリに反映済み(B-18。コミット1f603af)。stg2は未反映】2026-10-09 時点で、mode=x を csrf 改ざん・無しで送ると、まだ403にならない。
+(元の記載)【要修正】mode が許可値以外のときも、csrf検証を行うか、再計算を許可値のときだけにする。CSRFなしで、注文の支払日を書き換えられる恐れ。※実機で一部確認(2026-10-08): mode=x を csrf_token 改ざん・無しで送ると、403にならず処理された。注文が未入金だったため、再計算で値は変わらなかった(入金済の注文では、payment_date が上書きされる見込み。実在の会員の注文では試していない)。</t>
   </si>
 </sst>
 </file>
@@ -3121,16 +3138,16 @@
         <v>231</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3138,10 +3155,10 @@
         <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>228</v>
@@ -3150,7 +3167,7 @@
         <v>229</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3158,10 +3175,10 @@
         <v>32</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>228</v>
@@ -3170,7 +3187,7 @@
         <v>229</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3181,16 +3198,16 @@
         <v>217</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3201,16 +3218,16 @@
         <v>205</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3218,10 +3235,10 @@
         <v>44</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>228</v>
@@ -3230,7 +3247,7 @@
         <v>229</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3238,10 +3255,10 @@
         <v>48</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>228</v>
@@ -3250,7 +3267,7 @@
         <v>229</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" ht="99.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,19 +3275,19 @@
         <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3278,10 +3295,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>228</v>
@@ -3290,7 +3307,7 @@
         <v>229</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3315,10 @@
         <v>57</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>228</v>
@@ -3310,7 +3327,7 @@
         <v>229</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" ht="42.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,10 +3335,10 @@
         <v>61</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>228</v>
@@ -3330,7 +3347,7 @@
         <v>229</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" ht="49.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,10 +3355,10 @@
         <v>63</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>228</v>
@@ -3350,7 +3367,7 @@
         <v>229</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,10 +3375,10 @@
         <v>65</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>228</v>
@@ -3370,7 +3387,7 @@
         <v>229</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,10 +3395,10 @@
         <v>69</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>228</v>
@@ -3390,7 +3407,7 @@
         <v>229</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,10 +3415,10 @@
         <v>72</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>228</v>
@@ -3410,7 +3427,7 @@
         <v>229</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3418,10 +3435,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>228</v>
@@ -3430,7 +3447,7 @@
         <v>229</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,10 +3455,10 @@
         <v>77</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>228</v>
@@ -3450,7 +3467,7 @@
         <v>229</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,10 +3475,10 @@
         <v>79</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>228</v>
@@ -3470,7 +3487,7 @@
         <v>229</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -3511,7 +3528,7 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3519,7 +3536,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3527,16 +3544,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" ht="56.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3544,13 +3561,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3558,13 +3575,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3572,13 +3589,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3586,13 +3603,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3600,13 +3617,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" ht="56.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3614,13 +3631,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" ht="75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3628,13 +3645,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/secure_report/XSS対応_手動テスト手順書.xlsx
+++ b/secure_report/XSS対応_手動テスト手順書.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="294">
   <si>
     <t>XSS対応 手動テスト手順書(メール送信・決済まわり)</t>
   </si>
@@ -825,7 +825,7 @@
     <t>[CMS]amount_order/info.php hidden項目</t>
   </si>
   <si>
-    <t>OKだけど別エラー</t>
+    <t>OK</t>
   </si>
   <si>
     <t>2026-10-08</t>
@@ -840,13 +840,12 @@
 ・mode にタグ付き文字列・x を送る: 通常画面のまま。画面に反映されない。
 【別エラー】mode が許可値以外(例: x)のとき、csrf_token が改ざん値・無しでも403にならず処理される(csrf検証は許可値のときだけ)。mode が空でなければ注文のステータス再計算(tbl_order の UPDATE)が走るため、CSRFなしで支払日が書き換わる恐れ(開発者向けメモ7番)。今回の注文は未入金のため、再計算しても値は変わらなかった。
 ※入金済に変更(mode=pay)の正規操作は未実施(メールが飛ぶため。2026-10-09に持ち越し)。
-【2026-10-09 再確認】開発側の修正(B-18。mode が指定されたら csrf を検証、許可値以外は処理しない)はリポジトリに入っているが、stg2 では未反映のまま: mode=x を csrf_token 改ざん・無しで送ると、まだ403にならず200で処理される。stg2への反映後に再確認する(それまで「OKだけど別エラー」のまま)。</t>
+【2026-10-09 再確認】開発側の修正(B-18。mode が指定されたら csrf を検証、許可値以外は処理しない)はリポジトリに入っているが、stg2 では未反映のまま: mode=x を csrf_token 改ざん・無しで送ると、まだ403にならず200で処理される。stg2への反映後に再確認する(それまで「OKだけど別エラー」のまま)。
+【2026-10-09 正規操作を実施】テスト注文(oid=2135265)で、mode=pay(入金済に変更)を正しいcsrf_tokenで1回送信。入金済に変わり、入金日が入った。エラー・内部パス等の漏れなし。確認後、mode=nopay(未入金に変更)で元の未入金に戻した。入金完了メール1通がテスト受講者宛に送信されたはず(本文の見え方は、受信箱で確認)。
+【2026-10-09 B-18 の反映を確認】開発側の修正(mode が指定されたら csrf を検証)が stg2 に反映された。mode=x を csrf_token 改ざん・無しで送ると403で終了。mode=タグ付き文字列+csrf改ざんも403。csrf が正しい mode=x は200で、処理されず状態も変わらない(未入金のまま)。mode=pay+csrf改ざんは従来どおり403。mode空+order_detail_id にタグ付き文字列は、反映なし・状態変化なし。→ 別エラーが解消したため OK に変更。</t>
   </si>
   <si>
     <t>[CMS]bank_upload csv_upload</t>
-  </si>
-  <si>
-    <t>OK</t>
   </si>
   <si>
     <t>2026-10-09</t>
@@ -859,7 +858,8 @@
 ・CSVの中身にHTMLタグ/=1+1/SVGを入れても、タグとして出る箇所なし。
 【別エラー】入金日が数字でないCSV(例: abc)を送ると500エラーになり、サーバー内部パスとスタックトレース(bank_upload/index.php:130 checkdate()のTypeError)が画面に出る(不具合まとめの[B-3]と同系統)。
 ※アップロードしたCSV(約10本)がサーバー上に残っている。削除は開発担当に依頼。
-【2026-10-09 再確認】別エラーは解消(B-15・B-20 がstg2に反映済み)。入金日が数字でないCSV(abc)は500にならず「入金日は「YYYY/MM/DD」の形式で…」のエラー表示。引用符の閉じ忘れ等(列数不正)は「列数が正しくありません。…4列で…」のエラー表示(「0件登録しました」は出ない)。→ OKに変更。</t>
+【2026-10-09 再確認】別エラーは解消(B-15・B-20 がstg2に反映済み)。入金日が数字でないCSV(abc)は500にならず「入金日は「YYYY/MM/DD」の形式で…」のエラー表示。引用符の閉じ忘れ等(列数不正)は「列数が正しくありません。…4列で…」のエラー表示(「0件登録しました」は出ない)。→ OKに変更。
+【2026-10-09 正常系を実施】テスト注文(注文ID 2026100810008・商品26313・金額0)に合うCSV1行を取り込み、「合計1件の銀行振込を登録しました。」と表示。エラー・内部パス等の漏れなし。入金完了メール1通がテスト受講者宛に送信されたはず(受信箱で確認)。その後、注文は「未入金に変更」で戻した。</t>
   </si>
   <si>
     <t>[CMS]bank_upload 表示</t>
@@ -906,7 +906,8 @@
 ・temp_date / temp_no は未実施: 有効なcsrf_tokenで送ると、0円カートではそのまま注文が作られ無料の完了処理に進むため(メール系のため2026-10-09に持ち越し)。ソース上は、SQLにそのまま連結されている(order_regist.php:178,229)。
 ・payment_type: 0円カートでは12に上書きされるため、改ざんが効かず検証にならない。check: 画面側で使われていない。
 【2026-10-09 再確認】開発側の修正(B-17。temp_date・temp_no を数字だけに限定)がstg2に反映済み。temp_no=数字以外、temp_date=タグ付き・数字以外、シングルクォート入り、空、配列(temp_no[]・temp_date[])を、有効なcsrf_tokenで order_regist.php に送ったところ、すべて「決済エラー」の固定画面で拒否された(値は画面に出ない・内部パス等の漏れなし)。→ 未実施だった temp_date・temp_no の確認が完了したためOKに変更。
-※確認中、重複キー(temp_no=1&amp;temp_no=2。配列ではない)を1回送ってしまい、有効な値として通り、注文の仮データ(tbl_order_temp。order_no 202610092・0円)が1件作られた(完了処理には進めていない・メールなし)。</t>
+※確認中、重複キー(temp_no=1&amp;temp_no=2。配列ではない)を1回送ってしまい、有効な値として通り、注文の仮データ(tbl_order_temp。order_no 202610092・0円)が1件作られた(完了処理には進めていない・メールなし)。
+【2026-10-09 完了まで実施】0円の会場研修(pid 26314)を、order_regist.php から無料の完了処理まで進め、完了画面(end_free.php)に到達。エラー・内部パス等の漏れなし。申込完了メール1通がテスト受講者宛に送信されたはず(受信箱で確認)。注文番号 2026100910001 の申込が1件できている(定員30のうち1枠を使用)。</t>
   </si>
   <si>
     <t>settlement/index.php 表示</t>
@@ -1069,7 +1070,7 @@
     <t>alflearning/alflearning-cms/alfproduct/amount_order/info.php:94-96(csrf検証は許可値のみ)、:211-371(mode が空でなければ再計算)</t>
   </si>
   <si>
-    <t xml:space="preserve">【修正はリポジトリに反映済み(B-18。コミット1f603af)。stg2は未反映】2026-10-09 時点で、mode=x を csrf 改ざん・無しで送ると、まだ403にならない。
+    <t xml:space="preserve">【修正済み(B-18。コミット1f603af)】stg2に反映済みを確認(2026-10-09)。mode=x を csrf 改ざん・無しで送ると403になる。
 (元の記載)【要修正】mode が許可値以外のときも、csrf検証を行うか、再計算を許可値のときだけにする。CSRFなしで、注文の支払日を書き換えられる恐れ。※実機で一部確認(2026-10-08): mode=x を csrf_token 改ざん・無しで送ると、403にならず処理された。注文が未入金だったため、再計算で値は変わらなかった(入金済の注文では、payment_date が上書きされる見込み。実在の会員の注文では試していない)。</t>
   </si>
 </sst>
@@ -3138,16 +3139,16 @@
         <v>231</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3155,10 +3156,10 @@
         <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>235</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>236</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>228</v>
@@ -3167,7 +3168,7 @@
         <v>229</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3175,10 +3176,10 @@
         <v>32</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>228</v>
@@ -3187,7 +3188,7 @@
         <v>229</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3198,16 +3199,16 @@
         <v>217</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3218,16 +3219,16 @@
         <v>205</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3235,10 +3236,10 @@
         <v>44</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>228</v>
@@ -3247,7 +3248,7 @@
         <v>229</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3255,10 +3256,10 @@
         <v>48</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>228</v>
@@ -3267,7 +3268,7 @@
         <v>229</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" ht="99.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,19 +3276,19 @@
         <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,10 +3296,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>228</v>
@@ -3307,7 +3308,7 @@
         <v>229</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" ht="33.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3315,10 +3316,10 @@
         <v>57</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>228</v>
@@ -3327,7 +3328,7 @@
         <v>229</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" ht="42.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3335,10 +3336,10 @@
         <v>61</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>228</v>
@@ -3347,7 +3348,7 @@
         <v>229</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" ht="49.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3355,10 +3356,10 @@
         <v>63</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>228</v>
@@ -3367,7 +3368,7 @@
         <v>229</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3375,10 +3376,10 @@
         <v>65</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>228</v>
@@ -3387,7 +3388,7 @@
         <v>229</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,10 +3396,10 @@
         <v>69</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>228</v>
@@ -3407,7 +3408,7 @@
         <v>229</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3415,10 +3416,10 @@
         <v>72</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>228</v>
@@ -3427,7 +3428,7 @@
         <v>229</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,10 +3436,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>228</v>
@@ -3447,7 +3448,7 @@
         <v>229</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,10 +3456,10 @@
         <v>77</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>228</v>
@@ -3467,7 +3468,7 @@
         <v>229</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,10 +3476,10 @@
         <v>79</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>228</v>
@@ -3487,7 +3488,7 @@
         <v>229</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3528,7 +3529,7 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3536,7 +3537,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3544,16 +3545,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="4" ht="56.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3561,13 +3562,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3575,13 +3576,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3589,13 +3590,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3603,13 +3604,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>284</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3617,13 +3618,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>287</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="9" ht="56.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3631,13 +3632,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="10" ht="75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3645,24 +3646,24 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="56.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="84" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="27.95" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="56.1" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="27.95" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="84" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="27.95" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>

--- a/secure_report/XSS対応_手動テスト手順書.xlsx
+++ b/secure_report/XSS対応_手動テスト手順書.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="295">
   <si>
     <t>XSS対応 手動テスト手順書(メール送信・決済まわり)</t>
   </si>
@@ -919,10 +919,14 @@
     <t>payment_bank.php claim_flg</t>
   </si>
   <si>
+    <t>2026-10-12</t>
+  </si>
+  <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 claim_flg を送る注文確定の処理まで届かない。ソース上は、値がSQLのUPDATEにそのまま連結されている(payment_bank.php:145。開発者向けメモ参照)。
 【XSSの観点】ソース上は問題なし。claim_flg はCMSで ○/× の判定にしか使われず、値そのものは画面に出ない(amount_order/info.tpl・index.tpl)。決済画面(PC/スマホ)の動的な出力は、すべて |escape を通している。
-【2026-10-09】claim_flg のSQL連結は、開発側で 0・1 のみに限定済み(B-16)。stg2では、有料商品が無く到達できないため未確認。</t>
+【2026-10-09】claim_flg のSQL連結は、開発側で 0・1 のみに限定済み(B-16)。stg2では、有料商品が無く到達できないため未確認。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。claim_flgに `1' OR '1'='1` を直接POST。文字列完全一致チェックで0に丸められ、エラー・反映なし(B-16修正どおり)。</t>
   </si>
   <si>
     <t>payment_bank.php hidden項目</t>
@@ -935,7 +939,8 @@
   </si>
   <si>
     <t xml:space="preserve">有料商品が登録できず、銀行振込の画面(payment_bank.php)に到達できない。直接開くと(購入手続きの画面から来た形でも)「決済に失敗しました」だけが出て、商品名は表示されない。ソース上、商品名は |escape を通して出力。
-【XSSの観点】ソース上は問題なし。payment_bank.tpl(PC/スマホ)の動的な出力は、すべて |escape を通している。JS(onclick・script)内に動的な値はない。PHP側の直接出力(echo・print)もない。</t>
+【XSSの観点】ソース上は問題なし。payment_bank.tpl(PC/スマホ)の動的な出力は、すべて |escape を通している。JS(onclick・script)内に動的な値はない。PHP側の直接出力(echo・print)もない。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。stg2では注文作成直後に即「購入手続きが完了しました」になり、商品名表示を伴う入力待ち画面には到達しない(決済ゲートウェイ未連携の環境挙動とみられる)。ソース上も|escape済みで安全。</t>
   </si>
   <si>
     <t>payment_card.php card_no</t>
@@ -943,7 +948,8 @@
   <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 ソース上、エラー時の入力値の再表示は使われていない(コメントアウト済み)ため、カード番号は画面に反映されない見込み。
-【XSSの観点】ソース上は問題なし。payment_card.tpl(PC/スマホ)の動的な出力は、すべて |escape を通している。エラー時の入力値の再表示はコメントアウトされており、カード番号は画面に出ない。</t>
+【XSSの観点】ソース上は問題なし。payment_card.tpl(PC/スマホ)の動的な出力は、すべて |escape を通している。エラー時の入力値の再表示はコメントアウトされており、カード番号は画面に出ない。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。mode=settlement_exeでcard_noに`XCARD"&gt;&lt;svg/onload=alert(1)&gt;`を直接POST。200で応答、タグとして反映されず、エラーもなし。</t>
   </si>
   <si>
     <t>payment_card.php expire_m</t>
@@ -951,7 +957,8 @@
   <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 ソース上、エラー時の入力値の再表示は使われていない(コメントアウト済み)ため、有効期限(月)は画面に反映されない見込み。
-【XSSの観点】ソース上は問題なし。有効期限(月)は画面に出ない(再表示はコメントアウト)。年の選択肢(html_options)は、サーバー側で作る数値のみ。</t>
+【XSSの観点】ソース上は問題なし。有効期限(月)は画面に出ない(再表示はコメントアウト)。年の選択肢(html_options)は、サーバー側で作る数値のみ。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。同様にexpire_mへ`XEXPM&lt;script&gt;alert(1)&lt;/script&gt;`を送信。反映なし。</t>
   </si>
   <si>
     <t>payment_card.php expire_y</t>
@@ -959,7 +966,8 @@
   <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 ソース上、エラー時の入力値の再表示は使われていない(コメントアウト済み)ため、有効期限(年)は画面に反映されない見込み。
-【XSSの観点】ソース上は問題なし。有効期限(年)は画面に出ない(再表示はコメントアウト)。年の選択肢(html_options)は、サーバー側で作る数値のみ。</t>
+【XSSの観点】ソース上は問題なし。有効期限(年)は画面に出ない(再表示はコメントアウト)。年の選択肢(html_options)は、サーバー側で作る数値のみ。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。同様にexpire_yへ`XEXPY&lt;script&gt;alert(1)&lt;/script&gt;`を送信。反映なし。</t>
   </si>
   <si>
     <t>payment_card.php claim_flg</t>
@@ -968,7 +976,8 @@
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 claim_flg を送る処理まで届かない。ソース上は、値がSQLのUPDATEにそのまま連結されている(payment_card.php:164。開発者向けメモ参照)。
 【XSSの観点】ソース上は問題なし。claim_flg はCMSで ○/× の判定にしか使われず、値そのものは画面に出ない。決済画面(PC/スマホ)の動的な出力は、すべて |escape を通している。
-【2026-10-09】claim_flg のSQL連結は、開発側で 0・1 のみに限定済み(B-16)。stg2では、有料商品が無く到達できないため未確認。</t>
+【2026-10-09】claim_flg のSQL連結は、開発側で 0・1 のみに限定済み(B-16)。stg2では、有料商品が無く到達できないため未確認。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。claim_flgに`1' OR '1'='1`を直接POST。0に丸められ、エラー・反映なし。</t>
   </si>
   <si>
     <t>payment_card.php hidden項目</t>
@@ -976,14 +985,16 @@
   <si>
     <t xml:space="preserve">有料商品が登録できず(0円の商品のみ)、この画面に到達できない。0円のカートは注文確定後すぐ無料の完了処理(payment_free.php)へ進み、銀行振込・カードの画面は合計0円だと「決済に失敗しました」しか出ない(payment_bank.php / payment_card.php の total&gt;0 の確認)。有料商品が登録できるようになったら再実施する。
 payment_card.php は、注文の仮データが無いと csrf_token を検証しない(改ざん値でも403にならず失敗画面)。ソース上は、決済会社を呼ぶ前に検証する(payment_card.php:111)。
-【XSSの観点】ソース上は問題なし。payment_card.tpl(PC/スマホ)の動的な出力は、すべて |escape を通している。csrf_token は出力時にも |escape 済み。</t>
+【XSSの観点】ソース上は問題なし。payment_card.tpl(PC/スマホ)の動的な出力は、すべて |escape を通している。csrf_token は出力時にも |escape 済み。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。mode=settlement_exeを有効なorder_idに対して直接POSTしたが、エラー・不正遷移なし(C-0421の確認と合わせて安全)。</t>
   </si>
   <si>
     <t>payment_card.php 表示</t>
   </si>
   <si>
     <t xml:space="preserve">有料商品が登録できず、カードの画面(payment_card.php)に到達できない。直接開くと「決済に失敗しました」だけが出て、商品名は表示されない。ソース上、商品名は |escape を通して出力。
-【XSSの観点】ソース上は問題なし。payment_card.tpl(PC/スマホ)の商品名は |escape を通している。JS内に動的な値はなく、PHP側の直接出力もない。</t>
+【XSSの観点】ソース上は問題なし。payment_card.tpl(PC/スマホ)の商品名は |escape を通している。JS内に動的な値はなく、PHP側の直接出力もない。
+2026-10-12 有料商品が登録できないという前提が誤りと判明したため再実施(有料のproduct_live商品 pid=26333・1000円を新規登録しカートに投入、実機で購入手続きを完了)。C-0422と同様、stg2では即完了扱いとなり表示状態に到達しないが、実POSTでも漏れなし。ソース上も|escape済み。</t>
   </si>
   <si>
     <t>開発者向けメモ(修正が必要そうなもの。テスターは読まなくてよい)</t>
@@ -3319,16 +3330,16 @@
         <v>249</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" ht="42.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3336,7 +3347,7 @@
         <v>61</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>227</v>
@@ -3348,7 +3359,7 @@
         <v>229</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" ht="49.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3356,19 +3367,19 @@
         <v>63</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3376,19 +3387,19 @@
         <v>65</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3396,19 +3407,19 @@
         <v>69</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3416,19 +3427,19 @@
         <v>72</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3436,19 +3447,19 @@
         <v>74</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3456,19 +3467,19 @@
         <v>77</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3476,19 +3487,19 @@
         <v>79</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -3529,7 +3540,7 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3537,7 +3548,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3545,16 +3556,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" ht="56.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3562,13 +3573,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3576,13 +3587,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3590,13 +3601,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3604,13 +3615,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3618,13 +3629,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" ht="56.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3632,13 +3643,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" ht="75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3646,24 +3657,24 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="27.95" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="56.1" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="27.95" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="84" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="27.95" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="56.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="84" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
